--- a/data/input/Low Level Field Detail Design.xlsx
+++ b/data/input/Low Level Field Detail Design.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29423"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://btgroupcloud.sharepoint.com/teams/CampaignManagementTransformation/Shared Documents/ROI and Attribution/2. Data Design &amp; Engineering/3. Designs (Inc. Mapping Sheets)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EE2A327-3219-4924-A1CC-3B940C762241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B903C8BD-07FB-45A3-AF0F-13E648F6DB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="719" firstSheet="1" activeTab="1" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="719" firstSheet="6" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
   </bookViews>
   <sheets>
     <sheet name="objects" sheetId="1" r:id="rId1"/>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="1021">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="1021">
   <si>
     <t>Name</t>
   </si>
@@ -315,109 +315,29 @@
     <t>Order</t>
   </si>
   <si>
-    <t>Campaigns</t>
+    <t>Interactions</t>
   </si>
   <si>
     <t>Source System</t>
   </si>
   <si>
-    <t>A group of marketing activities designed to support a specific business objective or overaching message.</t>
-  </si>
-  <si>
-    <t>May be used to influence attribution wieghting as contains metadata that might indicate how relevant the content was for the linked outcome.</t>
-  </si>
-  <si>
-    <t>Use for comparing campaign performance.
-Used for filtering to activity within a specific campaign or attribute of campaign.</t>
-  </si>
-  <si>
-    <t>This is defined by the use of monday.com to generate a grouping.
-each Campaign should have a unique Monday Code.
-Iideally each campaign should have a clear and distinct audience. Be aligned to a single objective.
-We expect Asset reuse to be contained to a single campaign.
-Campaigns may superseed each other if there is a singificant overhall of content or delivery machanisms. In this case there would be multiple Rows representing each version of the campaign.</t>
+    <t>Tracked activities by individuals that show they are engaging with an Asset.</t>
+  </si>
+  <si>
+    <t>This Justifies that the marketing activity was engaged with by the individual and so supports the implication that thier buying decision was influenced by the result.
+Greater strength of interaction with marketing activity can be used for increased attribution of outcome to that activity.</t>
+  </si>
+  <si>
+    <t>This may be used for more targeted and channel specific assets engagement reporting.</t>
+  </si>
+  <si>
+    <t>Each row links one person to one activity. There may be multiple interactions for a person to an Activity</t>
   </si>
   <si>
     <t>y</t>
   </si>
   <si>
-    <t>bps_roi_ro/DSS(Archect review Qlik)</t>
-  </si>
-  <si>
-    <t>MVP-2</t>
-  </si>
-  <si>
-    <t>Channels</t>
-  </si>
-  <si>
-    <t>MRD</t>
-  </si>
-  <si>
-    <t>A method of Delivering Content/assets to customers. E.G. Email.</t>
-  </si>
-  <si>
-    <t>May be used to generalise and estimate the proportion of outcomes attributed back to activity.</t>
-  </si>
-  <si>
-    <t>Use for comparison and filtering on dashboards to compare between channels and compare within a channel.</t>
-  </si>
-  <si>
-    <t>Each channel represents a different way the customer experiances recieving the Asset.
-This is a reference table So each channel should be agreed and defined, This should be technology agnostic from BT delivery method. But might be technology relevant for delivery platform, Where BT has control.
-That is each Social Media platform is a different channel, Within those Ads Vs Organic Would be a different channel.
-But within Email there wouldn’t be different channels for the different email clients a person may recieve an email with.</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Facilitation Tool</t>
-  </si>
-  <si>
-    <t>A BT tool that facilitates the delivery of content/asssets to the Customers.</t>
-  </si>
-  <si>
-    <t>Attribution shouldn’t use this information.</t>
-  </si>
-  <si>
-    <t>Usefuly for Comparison and Filtering, So understand perfomance of similar channels and campaigns across different platforms. And to Understand within platforms performance.</t>
-  </si>
-  <si>
-    <t>Each row Represents a single platform. This is a reference table.
-Some decisions need to be made as to how platform bundles and addons should be Represented.
-Suggest each row represents the complete tool. All the elements accessible from a single interface/Has a seperate contract/cost/Would be expected to be used by the same person.</t>
-  </si>
-  <si>
-    <t>Marketing Assets</t>
-  </si>
-  <si>
-    <t>This is a piece of content or experiance that would be expected to be engaged with at a single point in time.</t>
-  </si>
-  <si>
-    <t>Useful for comparison within a particular channel to find find grain improvements</t>
-  </si>
-  <si>
-    <t>Each Row Represents a single piece of content, This may be an email, article, event. Some channel specific examples.
-Short events / Webinars might be one asset, Longer Events may be split into session.
-Variations of an email that share a meaningfully different message would be seperate assets. But emails that differ only in personalisation changes would be one asset.
-An assets should be something that everyone experiances the same way. No two people should have meaningfully different experiances with that asset.</t>
-  </si>
-  <si>
-    <t>Audience</t>
-  </si>
-  <si>
-    <t>A set of chriteria that defined a group of people who might be targeted for a communication or may be expected to be influenced by an asset.</t>
-  </si>
-  <si>
-    <t>Purpose here is to provide a linking methodology for Assets where direct influence to individuals is not possible due to the delivery channel.</t>
-  </si>
-  <si>
-    <t>Not used for Analytics</t>
-  </si>
-  <si>
-    <t>A specific and complete set of criteria would be contained in a single row. This same audience may be utilised by multiple assets or channels. This wouldn’t result in multiple Audience rows.
-Multiple audiences criteria may have overlapping members.
-And audience respresents the complete criteria a communicatino wouldn’t go to some intersection of two audiences, This example would be a third audience.</t>
+    <t>MVP-1</t>
   </si>
   <si>
     <t>Marketing Activity</t>
@@ -442,44 +362,21 @@
 Given the audience is Unknown one row here might have multiple engagements from Multiple Individuals or Companies.</t>
   </si>
   <si>
-    <t>MVP-1</t>
-  </si>
-  <si>
-    <t>Interactions</t>
-  </si>
-  <si>
-    <t>Tracked activities by individuals that show they are engaging with an Asset.</t>
-  </si>
-  <si>
-    <t>This Justifies that the marketing activity was engaged with by the individual and so supports the implication that thier buying decision was influenced by the result.
-Greater strength of interaction with marketing activity can be used for increased attribution of outcome to that activity.</t>
-  </si>
-  <si>
-    <t>This may be used for more targeted and channel specific assets engagement reporting.</t>
-  </si>
-  <si>
-    <t>Each row links one person to one activity. There may be multiple interactions for a person to an Activity</t>
-  </si>
-  <si>
-    <t>Attribution Linking Table</t>
-  </si>
-  <si>
-    <t>Derived</t>
-  </si>
-  <si>
-    <t>The cross reference table between the Marketing Activity and Outcome Tables.</t>
-  </si>
-  <si>
-    <t>This contains the raw relationships that could be attributed.</t>
-  </si>
-  <si>
-    <t>Not useful for Other Analytical purposes.</t>
-  </si>
-  <si>
-    <t>Each Row represents the relationship between an outcome and an activity for a Given model.</t>
-  </si>
-  <si>
-    <t>Dependant</t>
+    <t>Orders</t>
+  </si>
+  <si>
+    <t>Point in Time revenue generating events related to a specific company and product.</t>
+  </si>
+  <si>
+    <t>This is an outcome to be attributed to influence activities.</t>
+  </si>
+  <si>
+    <t>Used to show the attributed outcomes</t>
+  </si>
+  <si>
+    <t>Each Row should be a single product, sold at a specific point in time, to a specific company.
+Order of multiple units could be grouped to a single row.
+Mutiple different products sold at the same time to the same company as part of a single purchase event should still be different rows.</t>
   </si>
   <si>
     <t>Person</t>
@@ -543,21 +440,160 @@
     <t>N</t>
   </si>
   <si>
-    <t>Orders</t>
-  </si>
-  <si>
-    <t>Point in Time revenue generating events related to a specific company and product.</t>
-  </si>
-  <si>
-    <t>This is an outcome to be attributed to influence activities.</t>
-  </si>
-  <si>
-    <t>Used to show the attributed outcomes</t>
-  </si>
-  <si>
-    <t>Each Row should be a single product, sold at a specific point in time, to a specific company.
-Order of multiple units could be grouped to a single row.
-Mutiple different products sold at the same time to the same company as part of a single purchase event should still be different rows.</t>
+    <t>Dependant</t>
+  </si>
+  <si>
+    <t>Attribution Linking Table</t>
+  </si>
+  <si>
+    <t>Derived</t>
+  </si>
+  <si>
+    <t>The cross reference table between the Marketing Activity and Outcome Tables.</t>
+  </si>
+  <si>
+    <t>This contains the raw relationships that could be attributed.</t>
+  </si>
+  <si>
+    <t>Not useful for Other Analytical purposes.</t>
+  </si>
+  <si>
+    <t>Each Row represents the relationship between an outcome and an activity for a Given model.</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>Describes the BT Product Catelogue at different levels and contains the hierachy of products</t>
+  </si>
+  <si>
+    <t>Enables linking of both marketing activity and outcomes to the same products for relevance matching.</t>
+  </si>
+  <si>
+    <t>Used for comparing and filtering across all levels.</t>
+  </si>
+  <si>
+    <t>Each Row represents a product or group or family, All levels of heirachy are contained.</t>
+  </si>
+  <si>
+    <t>Attribution Model Output Table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science Team </t>
+  </si>
+  <si>
+    <t>Percentages that a model has assigned as the impact of a marketing activity to an outcome.</t>
+  </si>
+  <si>
+    <t>This is the Main output for the attribution modelling</t>
+  </si>
+  <si>
+    <t>Core to all attribution metrics</t>
+  </si>
+  <si>
+    <t>Each Row represents a single marketing activity linked to a single outcome for a particular model.
+There may be multiple models that have assigned different attribution levels for the same marketing activity to the same outcome element.
+Within a single model there would neven be multiple entries for the same marketing activity and outcome element interaction.
+Not every marketing activity will be linked to event outcome element.</t>
+  </si>
+  <si>
+    <t>Campaigns</t>
+  </si>
+  <si>
+    <t>A group of marketing activities designed to support a specific business objective or overaching message.</t>
+  </si>
+  <si>
+    <t>May be used to influence attribution wieghting as contains metadata that might indicate how relevant the content was for the linked outcome.</t>
+  </si>
+  <si>
+    <t>Use for comparing campaign performance.
+Used for filtering to activity within a specific campaign or attribute of campaign.</t>
+  </si>
+  <si>
+    <t>This is defined by the use of monday.com to generate a grouping.
+each Campaign should have a unique Monday Code.
+Iideally each campaign should have a clear and distinct audience. Be aligned to a single objective.
+We expect Asset reuse to be contained to a single campaign.
+Campaigns may superseed each other if there is a singificant overhall of content or delivery machanisms. In this case there would be multiple Rows representing each version of the campaign.</t>
+  </si>
+  <si>
+    <t>bps_roi_ro/DSS(Archect review Qlik)</t>
+  </si>
+  <si>
+    <t>MVP-2</t>
+  </si>
+  <si>
+    <t>Channels</t>
+  </si>
+  <si>
+    <t>MRD</t>
+  </si>
+  <si>
+    <t>A method of Delivering Content/assets to customers. E.G. Email.</t>
+  </si>
+  <si>
+    <t>May be used to generalise and estimate the proportion of outcomes attributed back to activity.</t>
+  </si>
+  <si>
+    <t>Use for comparison and filtering on dashboards to compare between channels and compare within a channel.</t>
+  </si>
+  <si>
+    <t>Each channel represents a different way the customer experiances recieving the Asset.
+This is a reference table So each channel should be agreed and defined, This should be technology agnostic from BT delivery method. But might be technology relevant for delivery platform, Where BT has control.
+That is each Social Media platform is a different channel, Within those Ads Vs Organic Would be a different channel.
+But within Email there wouldn’t be different channels for the different email clients a person may recieve an email with.</t>
+  </si>
+  <si>
+    <t>Facilitation Tool</t>
+  </si>
+  <si>
+    <t>A BT tool that facilitates the delivery of content/asssets to the Customers.</t>
+  </si>
+  <si>
+    <t>Attribution shouldn’t use this information.</t>
+  </si>
+  <si>
+    <t>Usefuly for Comparison and Filtering, So understand perfomance of similar channels and campaigns across different platforms. And to Understand within platforms performance.</t>
+  </si>
+  <si>
+    <t>Each row Represents a single platform. This is a reference table.
+Some decisions need to be made as to how platform bundles and addons should be Represented.
+Suggest each row represents the complete tool. All the elements accessible from a single interface/Has a seperate contract/cost/Would be expected to be used by the same person.</t>
+  </si>
+  <si>
+    <t>Marketing Assets</t>
+  </si>
+  <si>
+    <t>This is a piece of content or experiance that would be expected to be engaged with at a single point in time.</t>
+  </si>
+  <si>
+    <t>Useful for comparison within a particular channel to find find grain improvements</t>
+  </si>
+  <si>
+    <t>Each Row Represents a single piece of content, This may be an email, article, event. Some channel specific examples.
+Short events / Webinars might be one asset, Longer Events may be split into session.
+Variations of an email that share a meaningfully different message would be seperate assets. But emails that differ only in personalisation changes would be one asset.
+An assets should be something that everyone experiances the same way. No two people should have meaningfully different experiances with that asset.</t>
+  </si>
+  <si>
+    <t>Audience</t>
+  </si>
+  <si>
+    <t>A set of chriteria that defined a group of people who might be targeted for a communication or may be expected to be influenced by an asset.</t>
+  </si>
+  <si>
+    <t>Purpose here is to provide a linking methodology for Assets where direct influence to individuals is not possible due to the delivery channel.</t>
+  </si>
+  <si>
+    <t>Not used for Analytics</t>
+  </si>
+  <si>
+    <t>A specific and complete set of criteria would be contained in a single row. This same audience may be utilised by multiple assets or channels. This wouldn’t result in multiple Audience rows.
+Multiple audiences criteria may have overlapping members.
+And audience respresents the complete criteria a communicatino wouldn’t go to some intersection of two audiences, This example would be a third audience.</t>
   </si>
   <si>
     <t>Opportunities</t>
@@ -619,27 +655,6 @@
 If a company leaves as a BT and EE customer there would be two seperate rows for these events.</t>
   </si>
   <si>
-    <t>Attribution Model Output Table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science Team </t>
-  </si>
-  <si>
-    <t>Percentages that a model has assigned as the impact of a marketing activity to an outcome.</t>
-  </si>
-  <si>
-    <t>This is the Main output for the attribution modelling</t>
-  </si>
-  <si>
-    <t>Core to all attribution metrics</t>
-  </si>
-  <si>
-    <t>Each Row represents a single marketing activity linked to a single outcome for a particular model.
-There may be multiple models that have assigned different attribution levels for the same marketing activity to the same outcome element.
-Within a single model there would neven be multiple entries for the same marketing activity and outcome element interaction.
-Not every marketing activity will be linked to event outcome element.</t>
-  </si>
-  <si>
     <t>Attribution Model</t>
   </si>
   <si>
@@ -654,21 +669,6 @@
   <si>
     <t>Each Row represents an different model or iteration of a model.
 Model iterations would be where all the data has been recalculated with some meaningful change to input parameters.</t>
-  </si>
-  <si>
-    <t>Products</t>
-  </si>
-  <si>
-    <t>Describes the BT Product Catelogue at different levels and contains the hierachy of products</t>
-  </si>
-  <si>
-    <t>Enables linking of both marketing activity and outcomes to the same products for relevance matching.</t>
-  </si>
-  <si>
-    <t>Used for comparing and filtering across all levels.</t>
-  </si>
-  <si>
-    <t>Each Row represents a product or group or family, All levels of heirachy are contained.</t>
   </si>
   <si>
     <t>Date Dimension</t>
@@ -6816,22 +6816,22 @@
     <t>Self Identified / IP Inferred</t>
   </si>
   <si>
-    <t>Sales Meetings</t>
+    <t>Salesperson Meetings</t>
   </si>
   <si>
     <t>Sales</t>
   </si>
   <si>
-    <t>Sales Calls</t>
-  </si>
-  <si>
-    <t>Sales Email</t>
+    <t>Salesperson Calls</t>
+  </si>
+  <si>
+    <t>Salesperson Email</t>
   </si>
   <si>
     <t>Inbound Calls</t>
   </si>
   <si>
-    <t>Interactsion Concatnated</t>
+    <t>Interactions Concatenated</t>
   </si>
   <si>
     <t>Column1</t>
@@ -6852,18 +6852,78 @@
     <t>Column6</t>
   </si>
   <si>
-    <t>Column7</t>
-  </si>
-  <si>
     <t>Viewed</t>
   </si>
   <si>
+    <t>Sent</t>
+  </si>
+  <si>
+    <t>Received</t>
+  </si>
+  <si>
     <t>Clicked</t>
   </si>
   <si>
     <t>Submit Form</t>
   </si>
   <si>
+    <t>Bounced</t>
+  </si>
+  <si>
+    <t>Opened</t>
+  </si>
+  <si>
+    <t>Opt-Out</t>
+  </si>
+  <si>
+    <t>Responded</t>
+  </si>
+  <si>
+    <t>Registered</t>
+  </si>
+  <si>
+    <t>Attended</t>
+  </si>
+  <si>
+    <t>Called</t>
+  </si>
+  <si>
+    <t>Not Answered</t>
+  </si>
+  <si>
+    <t>Responsed</t>
+  </si>
+  <si>
+    <t>Initiated</t>
+  </si>
+  <si>
+    <t>Answered</t>
+  </si>
+  <si>
+    <t>Disconnected</t>
+  </si>
+  <si>
+    <t>Read</t>
+  </si>
+  <si>
+    <t>Dialled</t>
+  </si>
+  <si>
+    <t>Engaged</t>
+  </si>
+  <si>
+    <t>Invited</t>
+  </si>
+  <si>
+    <t>Attempted</t>
+  </si>
+  <si>
+    <t>Conversed</t>
+  </si>
+  <si>
+    <t>View on Demand</t>
+  </si>
+  <si>
     <t>Page View</t>
   </si>
   <si>
@@ -6877,66 +6937,6 @@
   </si>
   <si>
     <t>Live Chat?</t>
-  </si>
-  <si>
-    <t>Responded</t>
-  </si>
-  <si>
-    <t>Opt-Out</t>
-  </si>
-  <si>
-    <t>Registered</t>
-  </si>
-  <si>
-    <t>Attended</t>
-  </si>
-  <si>
-    <t>View on Demand</t>
-  </si>
-  <si>
-    <t>Sent</t>
-  </si>
-  <si>
-    <t>Received</t>
-  </si>
-  <si>
-    <t>Bounced</t>
-  </si>
-  <si>
-    <t>Read</t>
-  </si>
-  <si>
-    <t>Opened</t>
-  </si>
-  <si>
-    <t>Responsed</t>
-  </si>
-  <si>
-    <t>Invited</t>
-  </si>
-  <si>
-    <t>Dialled</t>
-  </si>
-  <si>
-    <t>Answered</t>
-  </si>
-  <si>
-    <t>Engaged</t>
-  </si>
-  <si>
-    <t>Called</t>
-  </si>
-  <si>
-    <t>Attempted</t>
-  </si>
-  <si>
-    <t>Conversed</t>
-  </si>
-  <si>
-    <t>Initiated</t>
-  </si>
-  <si>
-    <t>Disconnected</t>
   </si>
 </sst>
 </file>
@@ -7118,7 +7118,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7173,8 +7173,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -7331,11 +7337,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -7454,6 +7473,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7651,13 +7672,10 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{796020B2-92A8-4EA5-91A5-8AA3C83F36EA}" name="Table3" displayName="Table3" ref="A1:O22" totalsRowShown="0">
-  <autoFilter ref="A1:O22" xr:uid="{796020B2-92A8-4EA5-91A5-8AA3C83F36EA}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Interactions"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:O22" xr:uid="{796020B2-92A8-4EA5-91A5-8AA3C83F36EA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O22">
+    <sortCondition ref="O1:O22"/>
+  </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{2D15C978-230E-4A7E-BF65-A8F9B5B0BB26}" name="Name" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{3415CB41-1954-474C-9DE4-F2112710687F}" name="Generation Method"/>
@@ -7684,8 +7702,7 @@
   <autoFilter ref="A1:N237" xr:uid="{D396AB2F-F9BE-4F78-8BC5-51EC98BD60B1}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Attribution Linking Table"/>
-        <filter val="Channels"/>
+        <filter val="Company"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -7710,17 +7727,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D96477C-ECA9-4EBE-A35F-BB664900AC81}" name="Table2" displayName="Table2" ref="A1:J23" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A1:J23" xr:uid="{6D96477C-ECA9-4EBE-A35F-BB664900AC81}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Inbound Calls"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D96477C-ECA9-4EBE-A35F-BB664900AC81}" name="Table2" displayName="Table2" ref="A1:I23" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A1:I23" xr:uid="{6D96477C-ECA9-4EBE-A35F-BB664900AC81}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I23">
+    <sortCondition ref="A1:A23"/>
+  </sortState>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{EACA768A-938B-44E7-89E1-1321528ABE92}" name="Channel Name" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{C41B0F01-37EC-4C6A-ABBC-015577D1F75A}" name="Interactsion Concatnated" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{C41B0F01-37EC-4C6A-ABBC-015577D1F75A}" name="Interactions Concatenated" dataDxfId="1">
       <calculatedColumnFormula>_xlfn.TEXTJOIN(";",TRUE,C2:I2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{329D1A88-3265-4F13-8A3B-7827457D6F32}" name="Interactions"/>
@@ -7730,9 +7744,6 @@
     <tableColumn id="7" xr3:uid="{CA5A524F-838E-43AD-9CF2-84DFE3771ACC}" name="Column4"/>
     <tableColumn id="8" xr3:uid="{E6176540-475B-4EEA-94F4-70616D68E722}" name="Column5"/>
     <tableColumn id="9" xr3:uid="{CC2AC228-2DF6-4FF9-8A82-C7A0F3A6F6DD}" name="Column6" dataDxfId="0"/>
-    <tableColumn id="10" xr3:uid="{2A4CC5FF-AB1D-442B-92F9-F5CF06779A32}" name="Column7">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(A2,Channels!B:B,Channels!B:B,"MISSING",0,1)</calculatedColumnFormula>
-    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8286,11 +8297,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="72" hidden="1">
+    <row r="2" spans="1:15" ht="72">
       <c r="A2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -8302,212 +8313,227 @@
       <c r="E2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G2">
-        <f>COUNTIF(Attributes!A:A,objects!A2)</f>
-        <v>21</v>
+        <f>COUNTIF(Attributes!A:A,objects!A8)</f>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
       </c>
       <c r="I2">
+        <v>17</v>
+      </c>
+      <c r="J2">
+        <v>5000000</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2">
         <v>1</v>
       </c>
-      <c r="J2">
+    </row>
+    <row r="3" spans="1:15" ht="100.9">
+      <c r="A3" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3">
+        <f>COUNTIF(Attributes!A:A,objects!A7)</f>
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3">
+        <v>15</v>
+      </c>
+      <c r="J3">
+        <v>100000</v>
+      </c>
+      <c r="N3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="43.15">
+      <c r="A4" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="E4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4">
+        <f>COUNTIF(Attributes!A:A,objects!A13)</f>
+        <v>4</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4">
+        <v>9</v>
+      </c>
+      <c r="J4">
+        <v>700000</v>
+      </c>
+      <c r="N4" t="s">
         <v>22</v>
       </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="72" hidden="1">
-      <c r="A3" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3">
-        <f>COUNTIF(Attributes!A:A,objects!A3)</f>
-        <v>5</v>
-      </c>
-      <c r="H3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
-      <c r="N3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="72" hidden="1">
-      <c r="A4" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="O4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="57.6">
+      <c r="A5" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="B5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G4">
-        <f>COUNTIF(Attributes!A:A,objects!A4)</f>
+      <c r="E5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5">
+        <f>COUNTIF(Attributes!A:A,objects!A10)</f>
         <v>4</v>
       </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="57.6" hidden="1">
-      <c r="A5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="J5">
+        <v>500000</v>
+      </c>
+      <c r="N5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="86.45">
+      <c r="A6" s="29" t="s">
         <v>38</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5">
-        <f>COUNTIF(Attributes!A:A,objects!A5)</f>
-        <v>9</v>
-      </c>
-      <c r="H5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>300</v>
-      </c>
-      <c r="N5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="43.15" hidden="1">
-      <c r="A6" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="G6">
+        <f>COUNTIF(Attributes!A:A,objects!A11)</f>
+        <v>21</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>300000</v>
+      </c>
+      <c r="N6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="43.15">
+      <c r="A7" s="31" t="s">
         <v>43</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6">
-        <f>COUNTIF(Attributes!A:A,objects!A6)</f>
-        <v>8</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="100.9" hidden="1">
-      <c r="A7" s="29" t="s">
-        <v>45</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="G7">
+        <f>COUNTIF(Attributes!A:A,objects!A12)</f>
+        <v>5</v>
+      </c>
+      <c r="H7" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
         <v>49</v>
       </c>
-      <c r="G7">
-        <f>COUNTIF(Attributes!A:A,objects!A7)</f>
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>100000</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="O7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="O7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="72">
-      <c r="A8" s="29" t="s">
+      <c r="B8" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>52</v>
@@ -8522,108 +8548,105 @@
         <v>55</v>
       </c>
       <c r="G8">
-        <f>COUNTIF(Attributes!A:A,objects!A8)</f>
-        <v>13</v>
+        <f>COUNTIF(Attributes!A:A,objects!A9)</f>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="I8">
-        <v>17</v>
-      </c>
-      <c r="J8">
-        <v>5000000</v>
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>49</v>
       </c>
       <c r="N8" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="O8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" hidden="1">
-      <c r="A9" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="28.9">
+      <c r="A9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9">
+        <f>COUNTIF(Attributes!A:A,objects!A19)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9">
-        <f>COUNTIF(Attributes!A:A,objects!A9)</f>
-        <v>13</v>
-      </c>
-      <c r="H9" t="s">
-        <v>30</v>
-      </c>
       <c r="I9">
-        <v>18</v>
-      </c>
-      <c r="J9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="57.6">
+      <c r="A10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="N9" t="s">
-        <v>50</v>
-      </c>
-      <c r="O9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="57.6" hidden="1">
-      <c r="A10" s="29" t="s">
+      <c r="B10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="5" t="s">
         <v>67</v>
       </c>
       <c r="G10">
-        <f>COUNTIF(Attributes!A:A,objects!A10)</f>
+        <f>COUNTIF(Attributes!A:A,objects!A17)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10">
+        <v>19</v>
+      </c>
+      <c r="J10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10">
         <v>7</v>
       </c>
-      <c r="H10" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10">
-        <v>7</v>
-      </c>
-      <c r="J10">
-        <v>500000</v>
-      </c>
-      <c r="N10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="86.45" hidden="1">
+    </row>
+    <row r="11" spans="1:15" ht="72">
       <c r="A11" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="29" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -8635,320 +8658,309 @@
       <c r="E11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="4" t="s">
         <v>72</v>
       </c>
       <c r="G11">
-        <f>COUNTIF(Attributes!A:A,objects!A11)</f>
-        <v>50</v>
+        <f>COUNTIF(Attributes!A:A,objects!A2)</f>
+        <v>13</v>
       </c>
       <c r="H11" t="s">
         <v>21</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>300000</v>
+        <v>30</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="N11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="72">
+      <c r="A12" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12">
+        <f>COUNTIF(Attributes!A:A,objects!A3)</f>
+        <v>17</v>
+      </c>
+      <c r="H12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <f>COUNTA(Channels!B:B)-1</f>
+        <v>22</v>
+      </c>
+      <c r="N12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="72">
+      <c r="A13" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13">
+        <f>COUNTIF(Attributes!A:A,objects!A4)</f>
+        <v>33</v>
+      </c>
+      <c r="H13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="57.6">
+      <c r="A14" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14">
+        <f>COUNTIF(Attributes!A:A,objects!A5)</f>
+        <v>7</v>
+      </c>
+      <c r="H14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="J14">
+        <v>300</v>
+      </c>
+      <c r="N14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="43.15">
+      <c r="A15" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15">
+        <f>COUNTIF(Attributes!A:A,objects!A6)</f>
         <v>50</v>
       </c>
-      <c r="O11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="43.15" hidden="1">
-      <c r="A12" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="H15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15">
+        <v>5</v>
+      </c>
+      <c r="J15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="100.9">
+      <c r="A16" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16">
+        <f>COUNTIF(Attributes!A:A,objects!A14)</f>
+        <v>9</v>
+      </c>
+      <c r="H16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+      <c r="N16" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12">
-        <f>COUNTIF(Attributes!A:A,objects!A12)</f>
-        <v>5</v>
-      </c>
-      <c r="H12" t="s">
-        <v>78</v>
-      </c>
-      <c r="I12">
+    </row>
+    <row r="17" spans="1:14" ht="57.6">
+      <c r="A17" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17">
+        <f>COUNTIF(Attributes!A:A,objects!A15)</f>
         <v>8</v>
       </c>
-      <c r="J12" t="s">
-        <v>62</v>
-      </c>
-      <c r="O12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="43.15" hidden="1">
-      <c r="A13" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="H17" t="s">
+        <v>98</v>
+      </c>
+      <c r="I17">
+        <v>11</v>
+      </c>
+      <c r="N17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="43.15">
+      <c r="A18" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18">
+        <f>COUNTIF(Attributes!A:A,objects!A16)</f>
         <v>16</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13">
-        <f>COUNTIF(Attributes!A:A,objects!A13)</f>
-        <v>33</v>
-      </c>
-      <c r="H13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13">
-        <v>9</v>
-      </c>
-      <c r="J13">
-        <v>700000</v>
-      </c>
-      <c r="N13" t="s">
-        <v>50</v>
-      </c>
-      <c r="O13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="100.9" hidden="1">
-      <c r="A14" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G14">
-        <f>COUNTIF(Attributes!A:A,objects!A14)</f>
-        <v>16</v>
-      </c>
-      <c r="H14" t="s">
-        <v>87</v>
-      </c>
-      <c r="I14">
-        <v>10</v>
-      </c>
-      <c r="N14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="57.6" hidden="1">
-      <c r="A15" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G15">
-        <f>COUNTIF(Attributes!A:A,objects!A15)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" t="s">
-        <v>87</v>
-      </c>
-      <c r="I15">
-        <v>11</v>
-      </c>
-      <c r="N15" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="43.15" hidden="1">
-      <c r="A16" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16">
-        <f>COUNTIF(Attributes!A:A,objects!A16)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" t="s">
-        <v>87</v>
-      </c>
-      <c r="I16">
+      <c r="H18" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18">
         <v>12</v>
       </c>
-      <c r="N16" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="57.6" hidden="1">
-      <c r="A17" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G17">
-        <f>COUNTIF(Attributes!A:A,objects!A17)</f>
-        <v>4</v>
-      </c>
-      <c r="H17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17">
-        <v>19</v>
-      </c>
-      <c r="J17" t="s">
-        <v>62</v>
-      </c>
-      <c r="N17" t="s">
-        <v>50</v>
-      </c>
-      <c r="O17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="57.6" hidden="1">
-      <c r="A18" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="N18" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G18">
+    </row>
+    <row r="19" spans="1:14" ht="54.75" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G19">
         <f>COUNTIF(Attributes!A:A,objects!A18)</f>
         <v>0</v>
       </c>
-      <c r="H18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18">
+      <c r="H19" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19">
         <v>13</v>
       </c>
-      <c r="J18">
+      <c r="J19">
         <v>1</v>
       </c>
-      <c r="N18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="54.75" hidden="1" customHeight="1">
-      <c r="A19" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G19">
-        <f>COUNTIF(Attributes!A:A,objects!A19)</f>
-        <v>8</v>
-      </c>
-      <c r="H19" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
       <c r="N19" t="s">
-        <v>50</v>
-      </c>
-      <c r="O19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="28.9" hidden="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="28.9">
       <c r="A20" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>113</v>
@@ -8967,21 +8979,21 @@
         <v>7</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="N20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="43.15" hidden="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="43.15">
       <c r="A21" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>118</v>
@@ -8997,13 +9009,13 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="N21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="28.9" hidden="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="28.9">
       <c r="A22" s="2" t="s">
         <v>121</v>
       </c>
@@ -9027,10 +9039,10 @@
         <v>8</v>
       </c>
       <c r="H22" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="N22" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -9043,7 +9055,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
-  <dimension ref="A1:N238"/>
+  <dimension ref="A1:N237"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="29.140625" customWidth="1"/>
@@ -9105,9 +9117,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" hidden="1">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
         <v>138</v>
@@ -9128,9 +9140,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15">
+    <row r="3" spans="1:14" ht="15" hidden="1">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
         <v>143</v>
@@ -9151,9 +9163,9 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" hidden="1">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
         <v>147</v>
@@ -9169,9 +9181,9 @@
       </c>
       <c r="N4"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" hidden="1">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
         <v>150</v>
@@ -9187,9 +9199,9 @@
       </c>
       <c r="N5"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" hidden="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
         <v>153</v>
@@ -9205,9 +9217,9 @@
       </c>
       <c r="N6"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" hidden="1">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
         <v>156</v>
@@ -9223,9 +9235,9 @@
       </c>
       <c r="N7"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" hidden="1">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
         <v>159</v>
@@ -9241,9 +9253,9 @@
       </c>
       <c r="N8"/>
     </row>
-    <row r="9" spans="1:14" ht="107.25" customHeight="1">
+    <row r="9" spans="1:14" ht="107.25" hidden="1" customHeight="1">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
         <v>162</v>
@@ -9262,9 +9274,9 @@
       </c>
       <c r="N9"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" hidden="1">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
         <v>165</v>
@@ -9283,9 +9295,9 @@
       </c>
       <c r="N10"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" hidden="1">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
         <v>169</v>
@@ -9307,9 +9319,9 @@
       </c>
       <c r="N11"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" hidden="1">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
         <v>173</v>
@@ -9333,7 +9345,7 @@
     </row>
     <row r="13" spans="1:14" hidden="1">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
         <v>176</v>
@@ -9352,7 +9364,7 @@
     </row>
     <row r="14" spans="1:14" hidden="1">
       <c r="A14" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
         <v>138</v>
@@ -9371,7 +9383,7 @@
     </row>
     <row r="15" spans="1:14" hidden="1">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
         <v>181</v>
@@ -9390,7 +9402,7 @@
     </row>
     <row r="16" spans="1:14" hidden="1">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
         <v>183</v>
@@ -9570,7 +9582,7 @@
     </row>
     <row r="25" spans="1:11" customFormat="1" hidden="1">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s">
         <v>211</v>
@@ -9579,7 +9591,7 @@
     </row>
     <row r="26" spans="1:11" customFormat="1" hidden="1">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B26" t="s">
         <v>212</v>
@@ -9591,7 +9603,7 @@
     </row>
     <row r="27" spans="1:11" customFormat="1" hidden="1">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B27" t="s">
         <v>214</v>
@@ -9603,7 +9615,7 @@
     </row>
     <row r="28" spans="1:11" customFormat="1" hidden="1">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
         <v>216</v>
@@ -9615,7 +9627,7 @@
     </row>
     <row r="29" spans="1:11" customFormat="1" hidden="1">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
         <v>218</v>
@@ -9627,7 +9639,7 @@
     </row>
     <row r="30" spans="1:11" customFormat="1" hidden="1">
       <c r="A30" s="3" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>220</v>
@@ -9650,7 +9662,7 @@
     </row>
     <row r="31" spans="1:11" customFormat="1" hidden="1">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s">
         <v>224</v>
@@ -9662,7 +9674,7 @@
     </row>
     <row r="32" spans="1:11" customFormat="1" hidden="1">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B32" t="s">
         <v>226</v>
@@ -9674,7 +9686,7 @@
     </row>
     <row r="33" spans="1:10" customFormat="1" hidden="1">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s">
         <v>228</v>
@@ -9692,7 +9704,7 @@
     </row>
     <row r="34" spans="1:10" customFormat="1" hidden="1">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B34" t="s">
         <v>230</v>
@@ -9710,7 +9722,7 @@
     </row>
     <row r="35" spans="1:10" customFormat="1" hidden="1">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
         <v>232</v>
@@ -9728,7 +9740,7 @@
     </row>
     <row r="36" spans="1:10" customFormat="1" hidden="1">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
         <v>234</v>
@@ -9746,7 +9758,7 @@
     </row>
     <row r="37" spans="1:10" customFormat="1" hidden="1">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B37" t="s">
         <v>236</v>
@@ -9764,7 +9776,7 @@
     </row>
     <row r="38" spans="1:10" customFormat="1" hidden="1">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B38" t="s">
         <v>238</v>
@@ -9785,7 +9797,7 @@
     </row>
     <row r="39" spans="1:10" customFormat="1" hidden="1">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B39" t="s">
         <v>242</v>
@@ -9803,7 +9815,7 @@
     </row>
     <row r="40" spans="1:10" customFormat="1" hidden="1">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B40" t="s">
         <v>245</v>
@@ -9827,7 +9839,7 @@
     </row>
     <row r="41" spans="1:10" customFormat="1" hidden="1">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B41" t="s">
         <v>250</v>
@@ -9842,7 +9854,7 @@
     </row>
     <row r="42" spans="1:10" customFormat="1" hidden="1">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B42" t="s">
         <v>252</v>
@@ -9857,7 +9869,7 @@
     </row>
     <row r="43" spans="1:10" customFormat="1" hidden="1">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B43" t="s">
         <v>254</v>
@@ -9878,7 +9890,7 @@
     </row>
     <row r="44" spans="1:10" customFormat="1" ht="57.6" hidden="1">
       <c r="A44" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B44" t="s">
         <v>257</v>
@@ -9901,7 +9913,7 @@
     </row>
     <row r="45" spans="1:10" customFormat="1" hidden="1">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B45" t="s">
         <v>262</v>
@@ -9918,7 +9930,7 @@
     </row>
     <row r="46" spans="1:10" customFormat="1" hidden="1">
       <c r="A46" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B46" t="s">
         <v>265</v>
@@ -9933,7 +9945,7 @@
     </row>
     <row r="47" spans="1:10" customFormat="1" hidden="1">
       <c r="A47" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B47" t="s">
         <v>267</v>
@@ -9948,7 +9960,7 @@
     </row>
     <row r="48" spans="1:10" customFormat="1" hidden="1">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
         <v>268</v>
@@ -9966,7 +9978,7 @@
     </row>
     <row r="49" spans="1:14" hidden="1">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
         <v>271</v>
@@ -9985,7 +9997,7 @@
     </row>
     <row r="50" spans="1:14" hidden="1">
       <c r="A50" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B50" t="s">
         <v>274</v>
@@ -10001,7 +10013,7 @@
     </row>
     <row r="51" spans="1:14" hidden="1">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B51" t="s">
         <v>276</v>
@@ -10020,7 +10032,7 @@
     </row>
     <row r="52" spans="1:14" hidden="1">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B52" t="s">
         <v>279</v>
@@ -10039,7 +10051,7 @@
     </row>
     <row r="53" spans="1:14" hidden="1">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B53" t="s">
         <v>281</v>
@@ -10056,9 +10068,9 @@
       <c r="M53"/>
       <c r="N53"/>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" hidden="1">
       <c r="A54" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="B54" t="s">
         <v>284</v>
@@ -10078,9 +10090,9 @@
       <c r="M54"/>
       <c r="N54"/>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" hidden="1">
       <c r="A55" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="B55" t="s">
         <v>287</v>
@@ -10104,9 +10116,9 @@
         <v>290</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="57.6">
+    <row r="56" spans="1:14" ht="57.6" hidden="1">
       <c r="A56" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="B56" t="s">
         <v>291</v>
@@ -10129,9 +10141,9 @@
       <c r="M56"/>
       <c r="N56"/>
     </row>
-    <row r="57" spans="1:14" ht="43.15">
+    <row r="57" spans="1:14" ht="43.15" hidden="1">
       <c r="A57" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
         <v>214</v>
@@ -10151,9 +10163,9 @@
       <c r="M57"/>
       <c r="N57"/>
     </row>
-    <row r="58" spans="1:14" ht="28.9">
+    <row r="58" spans="1:14" ht="28.9" hidden="1">
       <c r="A58" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="B58" t="s">
         <v>297</v>
@@ -10173,9 +10185,9 @@
       <c r="M58"/>
       <c r="N58"/>
     </row>
-    <row r="59" spans="1:14" hidden="1">
+    <row r="59" spans="1:14">
       <c r="A59" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
         <v>276</v>
@@ -10192,9 +10204,9 @@
       <c r="M59"/>
       <c r="N59"/>
     </row>
-    <row r="60" spans="1:14" hidden="1">
+    <row r="60" spans="1:14">
       <c r="A60" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B60" t="s">
         <v>279</v>
@@ -10211,9 +10223,9 @@
       <c r="M60"/>
       <c r="N60"/>
     </row>
-    <row r="61" spans="1:14" hidden="1">
+    <row r="61" spans="1:14">
       <c r="A61" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B61" t="s">
         <v>281</v>
@@ -10230,9 +10242,9 @@
       <c r="M61"/>
       <c r="N61"/>
     </row>
-    <row r="62" spans="1:14" hidden="1">
+    <row r="62" spans="1:14">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B62" t="s">
         <v>156</v>
@@ -10247,9 +10259,9 @@
       <c r="M62"/>
       <c r="N62"/>
     </row>
-    <row r="63" spans="1:14" hidden="1">
+    <row r="63" spans="1:14">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B63" t="s">
         <v>301</v>
@@ -10264,9 +10276,9 @@
       <c r="M63"/>
       <c r="N63"/>
     </row>
-    <row r="64" spans="1:14" hidden="1">
+    <row r="64" spans="1:14">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B64" t="s">
         <v>302</v>
@@ -10289,9 +10301,9 @@
       <c r="M64"/>
       <c r="N64"/>
     </row>
-    <row r="65" spans="1:14" hidden="1">
+    <row r="65" spans="1:14">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B65" t="s">
         <v>307</v>
@@ -10314,9 +10326,9 @@
       <c r="M65"/>
       <c r="N65"/>
     </row>
-    <row r="66" spans="1:14" hidden="1">
+    <row r="66" spans="1:14">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B66" t="s">
         <v>311</v>
@@ -10336,9 +10348,9 @@
       <c r="M66"/>
       <c r="N66"/>
     </row>
-    <row r="67" spans="1:14" hidden="1">
+    <row r="67" spans="1:14">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>315</v>
@@ -10358,9 +10370,9 @@
       <c r="M67"/>
       <c r="N67"/>
     </row>
-    <row r="68" spans="1:14" ht="28.9" hidden="1">
+    <row r="68" spans="1:14" ht="28.9">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B68" t="s">
         <v>319</v>
@@ -10386,9 +10398,9 @@
       <c r="M68"/>
       <c r="N68"/>
     </row>
-    <row r="69" spans="1:14" hidden="1">
+    <row r="69" spans="1:14">
       <c r="A69" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B69" t="s">
         <v>324</v>
@@ -10408,9 +10420,9 @@
       <c r="M69"/>
       <c r="N69"/>
     </row>
-    <row r="70" spans="1:14" hidden="1">
+    <row r="70" spans="1:14">
       <c r="A70" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B70" t="s">
         <v>212</v>
@@ -10522,7 +10534,7 @@
     </row>
     <row r="78" spans="1:14" hidden="1">
       <c r="A78" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="B78" t="s">
         <v>212</v>
@@ -10538,7 +10550,7 @@
     </row>
     <row r="79" spans="1:14" hidden="1">
       <c r="A79" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="B79" t="s">
         <v>342</v>
@@ -10554,7 +10566,7 @@
     </row>
     <row r="80" spans="1:14" hidden="1">
       <c r="A80" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B80" t="s">
         <v>212</v>
@@ -10573,7 +10585,7 @@
     </row>
     <row r="81" spans="1:14" hidden="1">
       <c r="A81" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B81" t="s">
         <v>279</v>
@@ -10592,7 +10604,7 @@
     </row>
     <row r="82" spans="1:14" hidden="1">
       <c r="A82" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B82" t="s">
         <v>147</v>
@@ -10607,7 +10619,7 @@
     </row>
     <row r="83" spans="1:14" hidden="1">
       <c r="A83" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B83" t="s">
         <v>346</v>
@@ -10622,7 +10634,7 @@
     </row>
     <row r="84" spans="1:14" hidden="1">
       <c r="A84" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B84" t="s">
         <v>348</v>
@@ -10637,7 +10649,7 @@
     </row>
     <row r="85" spans="1:14" ht="41.45" hidden="1">
       <c r="A85" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B85" t="s">
         <v>350</v>
@@ -10658,7 +10670,7 @@
     </row>
     <row r="86" spans="1:14" hidden="1">
       <c r="A86" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B86" t="s">
         <v>354</v>
@@ -10676,7 +10688,7 @@
     </row>
     <row r="87" spans="1:14" hidden="1">
       <c r="A87" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B87" t="s">
         <v>143</v>
@@ -10694,7 +10706,7 @@
     </row>
     <row r="88" spans="1:14" hidden="1">
       <c r="A88" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B88" t="s">
         <v>359</v>
@@ -10712,7 +10724,7 @@
     </row>
     <row r="89" spans="1:14" hidden="1">
       <c r="A89" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B89" t="s">
         <v>361</v>
@@ -10730,7 +10742,7 @@
     </row>
     <row r="90" spans="1:14" ht="172.9" hidden="1">
       <c r="A90" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B90" t="s">
         <v>363</v>
@@ -10753,7 +10765,7 @@
     </row>
     <row r="91" spans="1:14" hidden="1">
       <c r="A91" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B91" t="s">
         <v>368</v>
@@ -10768,7 +10780,7 @@
     </row>
     <row r="92" spans="1:14" hidden="1">
       <c r="A92" s="2" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B92" t="s">
         <v>276</v>
@@ -10786,7 +10798,7 @@
     </row>
     <row r="93" spans="1:14" hidden="1">
       <c r="A93" s="2" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B93" t="s">
         <v>279</v>
@@ -10804,7 +10816,7 @@
     </row>
     <row r="94" spans="1:14" hidden="1">
       <c r="A94" s="2" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B94" t="s">
         <v>281</v>
@@ -10822,7 +10834,7 @@
     </row>
     <row r="95" spans="1:14" hidden="1">
       <c r="A95" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B95" t="s">
         <v>276</v>
@@ -10841,7 +10853,7 @@
     </row>
     <row r="96" spans="1:14" hidden="1">
       <c r="A96" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="B96" t="s">
         <v>370</v>
@@ -10857,7 +10869,7 @@
     </row>
     <row r="97" spans="1:14" hidden="1">
       <c r="A97" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B97" t="s">
         <v>143</v>
@@ -10876,7 +10888,7 @@
     </row>
     <row r="98" spans="1:14" hidden="1">
       <c r="A98" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B98" t="s">
         <v>373</v>
@@ -10901,7 +10913,7 @@
     </row>
     <row r="99" spans="1:14" hidden="1">
       <c r="A99" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B99" t="s">
         <v>378</v>
@@ -10926,7 +10938,7 @@
     </row>
     <row r="100" spans="1:14" hidden="1">
       <c r="A100" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B100" t="s">
         <v>380</v>
@@ -10945,7 +10957,7 @@
     </row>
     <row r="101" spans="1:14" hidden="1">
       <c r="A101" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B101" t="s">
         <v>382</v>
@@ -10964,7 +10976,7 @@
     </row>
     <row r="102" spans="1:14" hidden="1">
       <c r="A102" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B102" t="s">
         <v>385</v>
@@ -10986,7 +10998,7 @@
     </row>
     <row r="103" spans="1:14" hidden="1">
       <c r="A103" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B103" t="s">
         <v>388</v>
@@ -11005,7 +11017,7 @@
     </row>
     <row r="104" spans="1:14" hidden="1">
       <c r="A104" s="2" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B104" t="s">
         <v>284</v>
@@ -11024,7 +11036,7 @@
     </row>
     <row r="105" spans="1:14" hidden="1">
       <c r="A105" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B105" t="s">
         <v>228</v>
@@ -11043,7 +11055,7 @@
     </row>
     <row r="106" spans="1:14" hidden="1">
       <c r="A106" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B106" t="s">
         <v>211</v>
@@ -11065,7 +11077,7 @@
     </row>
     <row r="107" spans="1:14" hidden="1">
       <c r="A107" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B107" t="s">
         <v>281</v>
@@ -11084,7 +11096,7 @@
     </row>
     <row r="108" spans="1:14" hidden="1">
       <c r="A108" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B108" t="s">
         <v>398</v>
@@ -11103,7 +11115,7 @@
     </row>
     <row r="109" spans="1:14" hidden="1">
       <c r="A109" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B109" t="s">
         <v>236</v>
@@ -11122,7 +11134,7 @@
     </row>
     <row r="110" spans="1:14" hidden="1">
       <c r="A110" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B110" t="s">
         <v>234</v>
@@ -11141,7 +11153,7 @@
     </row>
     <row r="111" spans="1:14" hidden="1">
       <c r="A111" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="B111" t="s">
         <v>404</v>
@@ -11157,7 +11169,7 @@
     </row>
     <row r="112" spans="1:14" hidden="1">
       <c r="A112" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B112" t="s">
         <v>382</v>
@@ -11173,7 +11185,7 @@
     </row>
     <row r="113" spans="1:14" hidden="1">
       <c r="A113" s="3" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B113" t="s">
         <v>408</v>
@@ -11189,7 +11201,7 @@
     </row>
     <row r="114" spans="1:14" hidden="1">
       <c r="A114" s="3" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B114" t="s">
         <v>410</v>
@@ -11205,7 +11217,7 @@
     </row>
     <row r="115" spans="1:14" hidden="1">
       <c r="A115" s="3" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B115" t="s">
         <v>212</v>
@@ -11227,7 +11239,7 @@
     </row>
     <row r="116" spans="1:14" hidden="1">
       <c r="A116" s="3" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B116" t="s">
         <v>414</v>
@@ -11243,7 +11255,7 @@
     </row>
     <row r="117" spans="1:14" ht="57.6" hidden="1">
       <c r="A117" s="3" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B117" t="s">
         <v>268</v>
@@ -11268,7 +11280,7 @@
     </row>
     <row r="118" spans="1:14" hidden="1">
       <c r="A118" s="3" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B118" t="s">
         <v>276</v>
@@ -11286,7 +11298,7 @@
     </row>
     <row r="119" spans="1:14" hidden="1">
       <c r="A119" s="3" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B119" t="s">
         <v>279</v>
@@ -11304,7 +11316,7 @@
     </row>
     <row r="120" spans="1:14" hidden="1">
       <c r="A120" s="3" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B120" t="s">
         <v>281</v>
@@ -11322,7 +11334,7 @@
     </row>
     <row r="121" spans="1:14" hidden="1">
       <c r="A121" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B121" t="s">
         <v>419</v>
@@ -11341,7 +11353,7 @@
     </row>
     <row r="122" spans="1:14" hidden="1">
       <c r="A122" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B122" t="s">
         <v>212</v>
@@ -11363,7 +11375,7 @@
     </row>
     <row r="123" spans="1:14" hidden="1">
       <c r="A123" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B123" t="s">
         <v>232</v>
@@ -11382,7 +11394,7 @@
     </row>
     <row r="124" spans="1:14" hidden="1">
       <c r="A124" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B124" t="s">
         <v>424</v>
@@ -11401,7 +11413,7 @@
     </row>
     <row r="125" spans="1:14" s="3" customFormat="1" hidden="1">
       <c r="A125" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B125" t="s">
         <v>426</v>
@@ -11424,7 +11436,7 @@
     </row>
     <row r="126" spans="1:14" hidden="1">
       <c r="A126" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B126" t="s">
         <v>429</v>
@@ -11446,7 +11458,7 @@
     </row>
     <row r="127" spans="1:14" hidden="1">
       <c r="A127" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B127" t="s">
         <v>398</v>
@@ -11462,7 +11474,7 @@
     </row>
     <row r="128" spans="1:14" hidden="1">
       <c r="A128" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B128" t="s">
         <v>433</v>
@@ -11478,7 +11490,7 @@
     </row>
     <row r="129" spans="1:14" hidden="1">
       <c r="A129" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B129" t="s">
         <v>276</v>
@@ -11497,7 +11509,7 @@
     </row>
     <row r="130" spans="1:14" hidden="1">
       <c r="A130" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B130" t="s">
         <v>279</v>
@@ -11516,7 +11528,7 @@
     </row>
     <row r="131" spans="1:14" hidden="1">
       <c r="A131" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B131" t="s">
         <v>281</v>
@@ -11535,7 +11547,7 @@
     </row>
     <row r="132" spans="1:14" ht="28.9" hidden="1">
       <c r="A132" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B132" t="s">
         <v>435</v>
@@ -11554,7 +11566,7 @@
     </row>
     <row r="133" spans="1:14" ht="28.9" hidden="1">
       <c r="A133" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B133" t="s">
         <v>438</v>
@@ -11573,7 +11585,7 @@
     </row>
     <row r="134" spans="1:14" hidden="1">
       <c r="A134" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B134" t="s">
         <v>156</v>
@@ -11595,7 +11607,7 @@
     </row>
     <row r="135" spans="1:14" hidden="1">
       <c r="A135" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B135" t="s">
         <v>444</v>
@@ -11614,7 +11626,7 @@
     </row>
     <row r="136" spans="1:14" hidden="1">
       <c r="A136" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B136" t="s">
         <v>268</v>
@@ -11633,7 +11645,7 @@
     </row>
     <row r="137" spans="1:14" hidden="1">
       <c r="A137" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B137" t="s">
         <v>438</v>
@@ -11642,17 +11654,17 @@
         <v>449</v>
       </c>
       <c r="J137" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L137" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M137"/>
       <c r="N137"/>
     </row>
     <row r="138" spans="1:14" hidden="1">
       <c r="A138" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B138" t="s">
         <v>212</v>
@@ -11661,17 +11673,17 @@
         <v>450</v>
       </c>
       <c r="J138" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L138" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M138"/>
       <c r="N138"/>
     </row>
     <row r="139" spans="1:14" hidden="1">
       <c r="A139" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B139" t="s">
         <v>268</v>
@@ -11683,17 +11695,17 @@
         <v>452</v>
       </c>
       <c r="J139" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L139" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M139"/>
       <c r="N139"/>
     </row>
     <row r="140" spans="1:14" hidden="1">
       <c r="A140" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B140" t="s">
         <v>453</v>
@@ -11708,17 +11720,17 @@
         <v>456</v>
       </c>
       <c r="J140" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L140" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M140"/>
       <c r="N140"/>
     </row>
     <row r="141" spans="1:14" hidden="1">
       <c r="A141" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B141" t="s">
         <v>457</v>
@@ -11733,7 +11745,7 @@
         <v>459</v>
       </c>
       <c r="J141" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L141" t="s">
         <v>460</v>
@@ -11743,7 +11755,7 @@
     </row>
     <row r="142" spans="1:14" hidden="1">
       <c r="A142" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B142" t="s">
         <v>461</v>
@@ -11755,17 +11767,17 @@
         <v>463</v>
       </c>
       <c r="J142" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L142" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M142"/>
       <c r="N142"/>
     </row>
     <row r="143" spans="1:14" ht="28.9" hidden="1">
       <c r="A143" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B143" t="s">
         <v>464</v>
@@ -11780,17 +11792,17 @@
         <v>467</v>
       </c>
       <c r="J143" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L143" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M143"/>
       <c r="N143"/>
     </row>
     <row r="144" spans="1:14" hidden="1">
       <c r="A144" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B144" t="s">
         <v>468</v>
@@ -11802,17 +11814,17 @@
         <v>470</v>
       </c>
       <c r="J144" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L144" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M144"/>
       <c r="N144"/>
     </row>
     <row r="145" spans="1:14" hidden="1">
       <c r="A145" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B145" t="s">
         <v>471</v>
@@ -11822,17 +11834,17 @@
         <v>472</v>
       </c>
       <c r="J145" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L145" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M145"/>
       <c r="N145"/>
     </row>
     <row r="146" spans="1:14" hidden="1">
       <c r="A146" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B146" s="45" t="s">
         <v>473</v>
@@ -11842,17 +11854,17 @@
         <v>474</v>
       </c>
       <c r="J146" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L146" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M146"/>
       <c r="N146"/>
     </row>
     <row r="147" spans="1:14" hidden="1">
       <c r="A147" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B147" s="45" t="s">
         <v>475</v>
@@ -11862,17 +11874,17 @@
         <v>476</v>
       </c>
       <c r="J147" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L147" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M147"/>
       <c r="N147"/>
     </row>
     <row r="148" spans="1:14" hidden="1">
       <c r="A148" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B148" s="45" t="s">
         <v>477</v>
@@ -11882,17 +11894,17 @@
         <v>478</v>
       </c>
       <c r="J148" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L148" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M148"/>
       <c r="N148"/>
     </row>
     <row r="149" spans="1:14" hidden="1">
       <c r="A149" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B149" s="45" t="s">
         <v>479</v>
@@ -11902,18 +11914,18 @@
         <v>480</v>
       </c>
       <c r="J149" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="K149" s="15"/>
       <c r="L149" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M149"/>
       <c r="N149"/>
     </row>
     <row r="150" spans="1:14" hidden="1">
       <c r="A150" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B150" t="s">
         <v>481</v>
@@ -11928,17 +11940,17 @@
         <v>484</v>
       </c>
       <c r="J150" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L150" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M150"/>
       <c r="N150"/>
     </row>
     <row r="151" spans="1:14" hidden="1">
       <c r="A151" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B151" t="s">
         <v>485</v>
@@ -11953,17 +11965,17 @@
         <v>488</v>
       </c>
       <c r="J151" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L151" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M151"/>
       <c r="N151"/>
     </row>
     <row r="152" spans="1:14" hidden="1">
       <c r="A152" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B152" t="s">
         <v>489</v>
@@ -11978,17 +11990,17 @@
         <v>492</v>
       </c>
       <c r="J152" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L152" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M152"/>
       <c r="N152"/>
     </row>
     <row r="153" spans="1:14" ht="43.15" hidden="1">
       <c r="A153" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B153" t="s">
         <v>493</v>
@@ -12003,17 +12015,17 @@
         <v>496</v>
       </c>
       <c r="J153" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L153" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M153"/>
       <c r="N153"/>
     </row>
     <row r="154" spans="1:14" hidden="1">
       <c r="A154" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B154" t="s">
         <v>156</v>
@@ -12028,7 +12040,7 @@
         <v>498</v>
       </c>
       <c r="J154" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L154" t="s">
         <v>499</v>
@@ -12038,7 +12050,7 @@
     </row>
     <row r="155" spans="1:14" hidden="1">
       <c r="A155" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B155" t="s">
         <v>159</v>
@@ -12053,10 +12065,10 @@
         <v>501</v>
       </c>
       <c r="J155" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L155" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M155" s="50">
         <v>45952</v>
@@ -12067,7 +12079,7 @@
     </row>
     <row r="156" spans="1:14" hidden="1">
       <c r="A156" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B156" t="s">
         <v>503</v>
@@ -12079,17 +12091,17 @@
         <v>505</v>
       </c>
       <c r="J156" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L156" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M156"/>
       <c r="N156"/>
     </row>
     <row r="157" spans="1:14" hidden="1">
       <c r="A157" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B157" t="s">
         <v>506</v>
@@ -12104,17 +12116,17 @@
         <v>508</v>
       </c>
       <c r="J157" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L157" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M157"/>
       <c r="N157"/>
     </row>
     <row r="158" spans="1:14" hidden="1">
       <c r="A158" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B158" t="s">
         <v>509</v>
@@ -12129,17 +12141,17 @@
         <v>512</v>
       </c>
       <c r="J158" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L158" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M158"/>
       <c r="N158"/>
     </row>
     <row r="159" spans="1:14" hidden="1">
       <c r="A159" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B159" t="s">
         <v>513</v>
@@ -12151,17 +12163,17 @@
         <v>515</v>
       </c>
       <c r="J159" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L159" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M159"/>
       <c r="N159"/>
     </row>
     <row r="160" spans="1:14" hidden="1">
       <c r="A160" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B160" t="s">
         <v>516</v>
@@ -12176,17 +12188,17 @@
         <v>519</v>
       </c>
       <c r="J160" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L160" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M160"/>
       <c r="N160"/>
     </row>
     <row r="161" spans="1:14" hidden="1">
       <c r="A161" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B161" t="s">
         <v>520</v>
@@ -12198,17 +12210,17 @@
         <v>522</v>
       </c>
       <c r="J161" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L161" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M161"/>
       <c r="N161"/>
     </row>
     <row r="162" spans="1:14" hidden="1">
       <c r="A162" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B162" t="s">
         <v>523</v>
@@ -12217,20 +12229,20 @@
         <v>524</v>
       </c>
       <c r="G162" s="15" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="J162" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L162" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M162"/>
       <c r="N162"/>
     </row>
     <row r="163" spans="1:14" hidden="1">
       <c r="A163" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B163" t="s">
         <v>525</v>
@@ -12240,17 +12252,17 @@
         <v>526</v>
       </c>
       <c r="J163" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L163" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M163"/>
       <c r="N163"/>
     </row>
     <row r="164" spans="1:14" hidden="1">
       <c r="A164" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>527</v>
@@ -12262,17 +12274,17 @@
         <v>529</v>
       </c>
       <c r="J164" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L164" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M164"/>
       <c r="N164"/>
     </row>
     <row r="165" spans="1:14" hidden="1">
       <c r="A165" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>530</v>
@@ -12284,17 +12296,17 @@
         <v>532</v>
       </c>
       <c r="J165" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L165" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M165"/>
       <c r="N165"/>
     </row>
     <row r="166" spans="1:14" hidden="1">
       <c r="A166" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B166" t="s">
         <v>533</v>
@@ -12306,17 +12318,17 @@
         <v>535</v>
       </c>
       <c r="J166" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="L166" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M166"/>
       <c r="N166"/>
     </row>
     <row r="167" spans="1:14" hidden="1">
       <c r="A167" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B167" t="s">
         <v>276</v>
@@ -12331,17 +12343,17 @@
         <v>536</v>
       </c>
       <c r="J167" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L167" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M167"/>
       <c r="N167"/>
     </row>
     <row r="168" spans="1:14" hidden="1">
       <c r="A168" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B168" t="s">
         <v>279</v>
@@ -12356,17 +12368,17 @@
         <v>537</v>
       </c>
       <c r="J168" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L168" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M168"/>
       <c r="N168"/>
     </row>
     <row r="169" spans="1:14" hidden="1">
       <c r="A169" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B169" t="s">
         <v>281</v>
@@ -12381,17 +12393,17 @@
         <v>538</v>
       </c>
       <c r="J169" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L169" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M169"/>
       <c r="N169"/>
     </row>
     <row r="170" spans="1:14" hidden="1">
       <c r="A170" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B170" t="s">
         <v>159</v>
@@ -12413,7 +12425,7 @@
     </row>
     <row r="171" spans="1:14" hidden="1">
       <c r="A171" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B171" t="s">
         <v>542</v>
@@ -12430,7 +12442,7 @@
     </row>
     <row r="172" spans="1:14" hidden="1">
       <c r="A172" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B172" t="s">
         <v>544</v>
@@ -12449,7 +12461,7 @@
     </row>
     <row r="173" spans="1:14" hidden="1">
       <c r="A173" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B173" t="s">
         <v>276</v>
@@ -12471,7 +12483,7 @@
     </row>
     <row r="174" spans="1:14" hidden="1">
       <c r="A174" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B174" t="s">
         <v>279</v>
@@ -12493,7 +12505,7 @@
     </row>
     <row r="175" spans="1:14" hidden="1">
       <c r="A175" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B175" t="s">
         <v>281</v>
@@ -12515,7 +12527,7 @@
     </row>
     <row r="176" spans="1:14" hidden="1">
       <c r="A176" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B176" t="s">
         <v>156</v>
@@ -12530,7 +12542,7 @@
     </row>
     <row r="177" spans="1:14" hidden="1">
       <c r="A177" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B177" t="s">
         <v>159</v>
@@ -12550,7 +12562,7 @@
     </row>
     <row r="178" spans="1:14" hidden="1">
       <c r="A178" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B178" t="s">
         <v>156</v>
@@ -12567,7 +12579,7 @@
     </row>
     <row r="179" spans="1:14" hidden="1">
       <c r="A179" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B179" t="s">
         <v>234</v>
@@ -12586,7 +12598,7 @@
     </row>
     <row r="180" spans="1:14" hidden="1">
       <c r="A180" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B180" t="s">
         <v>236</v>
@@ -12605,7 +12617,7 @@
     </row>
     <row r="181" spans="1:14" hidden="1">
       <c r="A181" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B181" t="s">
         <v>554</v>
@@ -12624,7 +12636,7 @@
     </row>
     <row r="182" spans="1:14" hidden="1">
       <c r="A182" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="B182" t="s">
         <v>268</v>
@@ -12649,7 +12661,7 @@
     </row>
     <row r="183" spans="1:14" hidden="1">
       <c r="A183" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="B183" t="s">
         <v>559</v>
@@ -12671,7 +12683,7 @@
     </row>
     <row r="184" spans="1:14" hidden="1">
       <c r="A184" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="B184" t="s">
         <v>212</v>
@@ -12690,7 +12702,7 @@
     </row>
     <row r="185" spans="1:14" hidden="1">
       <c r="A185" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="B185" t="s">
         <v>564</v>
@@ -12712,7 +12724,7 @@
     </row>
     <row r="186" spans="1:14" hidden="1">
       <c r="A186" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="B186" t="s">
         <v>276</v>
@@ -12731,7 +12743,7 @@
     </row>
     <row r="187" spans="1:14" hidden="1">
       <c r="A187" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="B187" t="s">
         <v>279</v>
@@ -12750,7 +12762,7 @@
     </row>
     <row r="188" spans="1:14" hidden="1">
       <c r="A188" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="B188" t="s">
         <v>281</v>
@@ -12769,7 +12781,7 @@
     </row>
     <row r="189" spans="1:14" hidden="1">
       <c r="A189" s="2" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="B189" t="s">
         <v>567</v>
@@ -12809,10 +12821,10 @@
         <v>140</v>
       </c>
       <c r="J190" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="K190" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M190"/>
       <c r="N190"/>
@@ -12831,10 +12843,10 @@
         <v>393</v>
       </c>
       <c r="J191" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="K191" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M191"/>
       <c r="N191"/>
@@ -12853,10 +12865,10 @@
         <v>158</v>
       </c>
       <c r="J192" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="K192" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M192"/>
       <c r="N192"/>
@@ -12884,10 +12896,10 @@
         <v>579</v>
       </c>
       <c r="J193" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="K193" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M193"/>
       <c r="N193"/>
@@ -12912,10 +12924,10 @@
         <v>195</v>
       </c>
       <c r="J194" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="K194" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M194"/>
       <c r="N194"/>
@@ -12934,10 +12946,10 @@
         <v>397</v>
       </c>
       <c r="J195" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="K195" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M195"/>
       <c r="N195"/>
@@ -12956,10 +12968,10 @@
         <v>191</v>
       </c>
       <c r="J196" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="K196" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M196"/>
       <c r="N196"/>
@@ -12978,17 +12990,17 @@
         <v>191</v>
       </c>
       <c r="J197" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="K197" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="M197"/>
       <c r="N197"/>
     </row>
-    <row r="198" spans="1:14" ht="15">
+    <row r="198" spans="1:14" ht="15" hidden="1">
       <c r="A198" s="36" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B198" t="s">
         <v>287</v>
@@ -13004,9 +13016,9 @@
       </c>
       <c r="N198"/>
     </row>
-    <row r="199" spans="1:14" ht="28.9" hidden="1">
+    <row r="199" spans="1:14" ht="28.9">
       <c r="A199" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B199" t="s">
         <v>156</v>
@@ -13019,9 +13031,9 @@
       </c>
       <c r="M199"/>
     </row>
-    <row r="200" spans="1:14" hidden="1">
+    <row r="200" spans="1:14">
       <c r="A200" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B200" t="s">
         <v>588</v>
@@ -13037,9 +13049,9 @@
       </c>
       <c r="M200"/>
     </row>
-    <row r="201" spans="1:14" hidden="1">
+    <row r="201" spans="1:14">
       <c r="A201" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B201" t="s">
         <v>592</v>
@@ -13055,9 +13067,9 @@
       </c>
       <c r="M201"/>
     </row>
-    <row r="202" spans="1:14" hidden="1">
+    <row r="202" spans="1:14">
       <c r="A202" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B202" t="s">
         <v>595</v>
@@ -13073,9 +13085,9 @@
       </c>
       <c r="M202"/>
     </row>
-    <row r="203" spans="1:14" hidden="1">
+    <row r="203" spans="1:14">
       <c r="A203" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B203" t="s">
         <v>598</v>
@@ -13094,9 +13106,9 @@
       </c>
       <c r="M203"/>
     </row>
-    <row r="204" spans="1:14" hidden="1">
+    <row r="204" spans="1:14">
       <c r="A204" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B204" t="s">
         <v>602</v>
@@ -13112,9 +13124,9 @@
       </c>
       <c r="M204"/>
     </row>
-    <row r="205" spans="1:14" hidden="1">
+    <row r="205" spans="1:14">
       <c r="A205" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B205" t="s">
         <v>605</v>
@@ -13130,9 +13142,9 @@
       </c>
       <c r="M205"/>
     </row>
-    <row r="206" spans="1:14" hidden="1">
+    <row r="206" spans="1:14">
       <c r="A206" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B206" t="s">
         <v>608</v>
@@ -13148,9 +13160,9 @@
       </c>
       <c r="M206"/>
     </row>
-    <row r="207" spans="1:14" hidden="1">
+    <row r="207" spans="1:14">
       <c r="A207" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B207" t="s">
         <v>611</v>
@@ -13166,9 +13178,9 @@
       </c>
       <c r="M207"/>
     </row>
-    <row r="208" spans="1:14" hidden="1">
+    <row r="208" spans="1:14">
       <c r="A208" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B208" t="s">
         <v>613</v>
@@ -13184,9 +13196,9 @@
       </c>
       <c r="M208"/>
     </row>
-    <row r="209" spans="1:13" hidden="1">
+    <row r="209" spans="1:13">
       <c r="A209" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B209" t="s">
         <v>615</v>
@@ -13202,9 +13214,9 @@
       </c>
       <c r="M209"/>
     </row>
-    <row r="210" spans="1:13" hidden="1">
+    <row r="210" spans="1:13">
       <c r="A210" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B210" t="s">
         <v>617</v>
@@ -13220,9 +13232,9 @@
       </c>
       <c r="M210"/>
     </row>
-    <row r="211" spans="1:13" hidden="1">
+    <row r="211" spans="1:13">
       <c r="A211" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B211" t="s">
         <v>619</v>
@@ -13241,9 +13253,9 @@
       </c>
       <c r="M211"/>
     </row>
-    <row r="212" spans="1:13" hidden="1">
+    <row r="212" spans="1:13">
       <c r="A212" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B212" t="s">
         <v>623</v>
@@ -13256,9 +13268,9 @@
       </c>
       <c r="M212"/>
     </row>
-    <row r="213" spans="1:13" hidden="1">
+    <row r="213" spans="1:13">
       <c r="A213" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B213" t="s">
         <v>625</v>
@@ -13274,9 +13286,9 @@
       </c>
       <c r="M213"/>
     </row>
-    <row r="214" spans="1:13" ht="28.9" hidden="1">
+    <row r="214" spans="1:13" ht="28.9">
       <c r="A214" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B214" t="s">
         <v>628</v>
@@ -13292,9 +13304,9 @@
       </c>
       <c r="M214"/>
     </row>
-    <row r="215" spans="1:13" hidden="1">
+    <row r="215" spans="1:13">
       <c r="A215" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B215" t="s">
         <v>631</v>
@@ -13310,9 +13322,9 @@
       </c>
       <c r="M215"/>
     </row>
-    <row r="216" spans="1:13" hidden="1">
+    <row r="216" spans="1:13">
       <c r="A216" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B216" t="s">
         <v>635</v>
@@ -13328,9 +13340,9 @@
       </c>
       <c r="M216"/>
     </row>
-    <row r="217" spans="1:13" hidden="1">
+    <row r="217" spans="1:13">
       <c r="A217" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B217" t="s">
         <v>638</v>
@@ -13346,9 +13358,9 @@
       </c>
       <c r="M217"/>
     </row>
-    <row r="218" spans="1:13" hidden="1">
+    <row r="218" spans="1:13">
       <c r="A218" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B218" t="s">
         <v>641</v>
@@ -13364,9 +13376,9 @@
       </c>
       <c r="M218"/>
     </row>
-    <row r="219" spans="1:13" hidden="1">
+    <row r="219" spans="1:13">
       <c r="A219" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B219" t="s">
         <v>644</v>
@@ -13382,9 +13394,9 @@
       </c>
       <c r="M219"/>
     </row>
-    <row r="220" spans="1:13" hidden="1">
+    <row r="220" spans="1:13">
       <c r="A220" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B220" t="s">
         <v>646</v>
@@ -13400,9 +13412,9 @@
       </c>
       <c r="M220"/>
     </row>
-    <row r="221" spans="1:13" ht="28.9" hidden="1">
+    <row r="221" spans="1:13" ht="28.9">
       <c r="A221" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B221" t="s">
         <v>649</v>
@@ -13418,9 +13430,9 @@
       </c>
       <c r="M221"/>
     </row>
-    <row r="222" spans="1:13" hidden="1">
+    <row r="222" spans="1:13">
       <c r="A222" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B222" t="s">
         <v>652</v>
@@ -13439,9 +13451,9 @@
       </c>
       <c r="M222"/>
     </row>
-    <row r="223" spans="1:13" hidden="1">
+    <row r="223" spans="1:13">
       <c r="A223" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B223" t="s">
         <v>656</v>
@@ -13460,9 +13472,9 @@
       </c>
       <c r="M223"/>
     </row>
-    <row r="224" spans="1:13" hidden="1">
+    <row r="224" spans="1:13">
       <c r="A224" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B224" t="s">
         <v>658</v>
@@ -13478,9 +13490,9 @@
       </c>
       <c r="M224"/>
     </row>
-    <row r="225" spans="1:13" hidden="1">
+    <row r="225" spans="1:13">
       <c r="A225" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B225" t="s">
         <v>661</v>
@@ -13496,9 +13508,9 @@
       </c>
       <c r="M225"/>
     </row>
-    <row r="226" spans="1:13" hidden="1">
+    <row r="226" spans="1:13">
       <c r="A226" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B226" t="s">
         <v>663</v>
@@ -13514,9 +13526,9 @@
       </c>
       <c r="M226"/>
     </row>
-    <row r="227" spans="1:13" hidden="1">
+    <row r="227" spans="1:13">
       <c r="A227" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B227" t="s">
         <v>665</v>
@@ -13532,9 +13544,9 @@
       </c>
       <c r="M227"/>
     </row>
-    <row r="228" spans="1:13" hidden="1">
+    <row r="228" spans="1:13">
       <c r="A228" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B228" t="s">
         <v>668</v>
@@ -13550,9 +13562,9 @@
       </c>
       <c r="M228"/>
     </row>
-    <row r="229" spans="1:13" hidden="1">
+    <row r="229" spans="1:13">
       <c r="A229" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B229" t="s">
         <v>671</v>
@@ -13568,9 +13580,9 @@
       </c>
       <c r="M229"/>
     </row>
-    <row r="230" spans="1:13" hidden="1">
+    <row r="230" spans="1:13">
       <c r="A230" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B230" t="s">
         <v>674</v>
@@ -13586,9 +13598,9 @@
       </c>
       <c r="M230"/>
     </row>
-    <row r="231" spans="1:13" hidden="1">
+    <row r="231" spans="1:13">
       <c r="A231" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B231" t="s">
         <v>676</v>
@@ -13604,9 +13616,9 @@
       </c>
       <c r="M231"/>
     </row>
-    <row r="232" spans="1:13" hidden="1">
+    <row r="232" spans="1:13">
       <c r="A232" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B232" t="s">
         <v>678</v>
@@ -13622,9 +13634,9 @@
       </c>
       <c r="M232"/>
     </row>
-    <row r="233" spans="1:13" hidden="1">
+    <row r="233" spans="1:13">
       <c r="A233" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B233" t="s">
         <v>681</v>
@@ -13640,9 +13652,9 @@
       </c>
       <c r="M233"/>
     </row>
-    <row r="234" spans="1:13" hidden="1">
+    <row r="234" spans="1:13">
       <c r="A234" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B234" t="s">
         <v>683</v>
@@ -13658,9 +13670,9 @@
       </c>
       <c r="M234"/>
     </row>
-    <row r="235" spans="1:13" hidden="1">
+    <row r="235" spans="1:13">
       <c r="A235" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B235" t="s">
         <v>686</v>
@@ -13676,9 +13688,9 @@
       </c>
       <c r="M235"/>
     </row>
-    <row r="236" spans="1:13" hidden="1">
+    <row r="236" spans="1:13">
       <c r="A236" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B236" t="s">
         <v>688</v>
@@ -13694,9 +13706,9 @@
       </c>
       <c r="M236"/>
     </row>
-    <row r="237" spans="1:13">
+    <row r="237" spans="1:13" hidden="1">
       <c r="A237" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B237" t="s">
         <v>691</v>
@@ -13708,7 +13720,6 @@
         <v>585</v>
       </c>
     </row>
-    <row r="238" spans="1:13" ht="15"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J97">
     <sortCondition ref="A2:A97"/>
@@ -13782,7 +13793,7 @@
         <v>698</v>
       </c>
       <c r="G1" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>699</v>
@@ -13975,7 +13986,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>719</v>
@@ -14014,7 +14025,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>720</v>
@@ -14051,7 +14062,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>721</v>
@@ -14088,7 +14099,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>722</v>
@@ -15069,7 +15080,7 @@
         <v>941</v>
       </c>
       <c r="H2" t="str">
-        <f>_xlfn.XLOOKUP(B2,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B2,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Viewed;Clicked;Submit Form</v>
       </c>
       <c r="J2" t="s">
@@ -15096,7 +15107,7 @@
         <v>941</v>
       </c>
       <c r="H3" t="str">
-        <f>_xlfn.XLOOKUP(B3,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B3,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Viewed;Clicked;Submit Form</v>
       </c>
     </row>
@@ -15117,7 +15128,7 @@
         <v>941</v>
       </c>
       <c r="H4" t="str">
-        <f>_xlfn.XLOOKUP(B4,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B4,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Page View;Link Click;Submit Form;Watch Video;Download;Live Chat?</v>
       </c>
       <c r="J4" t="s">
@@ -15147,7 +15158,7 @@
         <v>941</v>
       </c>
       <c r="H5" t="str">
-        <f>_xlfn.XLOOKUP(B5,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B5,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Viewed</v>
       </c>
     </row>
@@ -15168,7 +15179,7 @@
         <v>941</v>
       </c>
       <c r="H6" t="str">
-        <f>_xlfn.XLOOKUP(B6,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B6,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Viewed;Clicked;Responded</v>
       </c>
     </row>
@@ -15189,7 +15200,7 @@
         <v>958</v>
       </c>
       <c r="H7" t="str">
-        <f>_xlfn.XLOOKUP(B7,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B7,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Viewed;Clicked;Responded;Opt-Out</v>
       </c>
     </row>
@@ -15210,7 +15221,7 @@
         <v>958</v>
       </c>
       <c r="H8" t="str">
-        <f>_xlfn.XLOOKUP(B8,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B8,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Registered;Attended;View on Demand</v>
       </c>
     </row>
@@ -15231,7 +15242,7 @@
         <v>958</v>
       </c>
       <c r="H9" t="str">
-        <f>_xlfn.XLOOKUP(B9,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B9,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Registered;Attended</v>
       </c>
     </row>
@@ -15249,7 +15260,7 @@
         <v>961</v>
       </c>
       <c r="H10" t="str">
-        <f>_xlfn.XLOOKUP(B10,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B10,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Registered;Attended;View on Demand</v>
       </c>
     </row>
@@ -15267,7 +15278,7 @@
         <v>952</v>
       </c>
       <c r="H11" t="str">
-        <f>_xlfn.XLOOKUP(B11,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B11,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Sent;Received;Bounced</v>
       </c>
       <c r="I11" t="b">
@@ -15288,7 +15299,7 @@
         <v>480</v>
       </c>
       <c r="H12" t="str">
-        <f>_xlfn.XLOOKUP(B12,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B12,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Sent;Received;Read;Clicked;Responded;Opt-Out</v>
       </c>
     </row>
@@ -15306,8 +15317,8 @@
         <v>480</v>
       </c>
       <c r="H13" t="str">
-        <f>_xlfn.XLOOKUP(B13,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
-        <v>Sent;Received;Read;Clicked;Responded;Opt-Out</v>
+        <f>_xlfn.XLOOKUP(B13,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
+        <v>Sent;Received;Read;Clicked;Responded;Opt-Out;Opened</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -15324,7 +15335,7 @@
         <v>480</v>
       </c>
       <c r="H14" t="str">
-        <f>_xlfn.XLOOKUP(B14,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B14,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Sent;Received;Bounced;Opened;Clicked;Opt-Out;Responded</v>
       </c>
       <c r="I14" t="b">
@@ -15351,7 +15362,7 @@
         <v>480</v>
       </c>
       <c r="H15" t="str">
-        <f>_xlfn.XLOOKUP(B15,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B15,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Sent;Received;Bounced;Clicked;Responsed;Opt-Out</v>
       </c>
       <c r="I15" t="b">
@@ -15378,7 +15389,7 @@
         <v>480</v>
       </c>
       <c r="H16" t="str">
-        <f>_xlfn.XLOOKUP(B16,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B16,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Sent;Received;Bounced;Clicked;Responsed;Opt-Out</v>
       </c>
     </row>
@@ -15396,7 +15407,7 @@
         <v>480</v>
       </c>
       <c r="H17" t="str">
-        <f>_xlfn.XLOOKUP(B17,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B17,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Sent;Received;Clicked</v>
       </c>
     </row>
@@ -15414,7 +15425,7 @@
         <v>976</v>
       </c>
       <c r="H18" t="str">
-        <f>_xlfn.XLOOKUP(B18,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B18,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Attempted;Answered;Conversed</v>
       </c>
       <c r="J18" t="s">
@@ -15438,7 +15449,7 @@
         <v>976</v>
       </c>
       <c r="H19" t="str">
-        <f>_xlfn.XLOOKUP(B19,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B19,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Initiated;Answered;Disconnected</v>
       </c>
       <c r="J19" t="s">
@@ -15449,7 +15460,7 @@
       </c>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" t="s">
+      <c r="B20" s="56" t="s">
         <v>980</v>
       </c>
       <c r="C20" t="s">
@@ -15462,12 +15473,12 @@
         <v>976</v>
       </c>
       <c r="H20" t="str">
-        <f>_xlfn.XLOOKUP(B20,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B20,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Invited;Attended</v>
       </c>
     </row>
     <row r="21" spans="2:11">
-      <c r="B21" t="s">
+      <c r="B21" s="56" t="s">
         <v>982</v>
       </c>
       <c r="C21" t="s">
@@ -15480,12 +15491,12 @@
         <v>976</v>
       </c>
       <c r="H21" t="str">
-        <f>_xlfn.XLOOKUP(B21,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B21,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Dialled;Answered;Engaged</v>
       </c>
     </row>
     <row r="22" spans="2:11">
-      <c r="B22" t="s">
+      <c r="B22" s="57" t="s">
         <v>983</v>
       </c>
       <c r="C22" t="s">
@@ -15498,7 +15509,7 @@
         <v>480</v>
       </c>
       <c r="H22" t="str">
-        <f>_xlfn.XLOOKUP(B22,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
+        <f>_xlfn.XLOOKUP(B22,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
         <v>Sent;Received;Bounced;Opened;Clicked;Opt-Out;Responded</v>
       </c>
     </row>
@@ -15519,8 +15530,8 @@
         <v>941</v>
       </c>
       <c r="H23" t="str">
-        <f>_xlfn.XLOOKUP(B23,Table2[Channel Name],Table2[Interactsion Concatnated],"",0,1)</f>
-        <v>Called</v>
+        <f>_xlfn.XLOOKUP(B23,Table2[Channel Name],Table2[Interactions Concatenated],"",0,1)</f>
+        <v>Called;Not Answered</v>
       </c>
       <c r="J23" t="s">
         <v>977</v>
@@ -15540,7 +15551,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAF728D-8DC4-43CB-A2BE-8E22F440F4CC}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
@@ -15550,10 +15561,9 @@
     <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
       <c r="A1" s="37" t="s">
         <v>929</v>
       </c>
@@ -15561,7 +15571,7 @@
         <v>985</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="D1" s="34" t="s">
         <v>986</v>
@@ -15581,40 +15591,27 @@
       <c r="I1" s="35" t="s">
         <v>991</v>
       </c>
-      <c r="J1" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" hidden="1">
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="41" t="s">
-        <v>938</v>
+        <v>951</v>
       </c>
       <c r="B2" s="38" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,C2:I2)</f>
-        <v>Viewed;Clicked;Submit Form</v>
+        <v>Viewed</v>
       </c>
       <c r="C2" t="s">
-        <v>993</v>
-      </c>
-      <c r="D2" t="s">
-        <v>994</v>
-      </c>
-      <c r="E2" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="I2" s="23"/>
-      <c r="J2" t="str">
-        <f>_xlfn.XLOOKUP(A2,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Paid Digital Ads</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" hidden="1">
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="41" t="s">
-        <v>944</v>
+        <v>974</v>
       </c>
       <c r="B3" s="39" t="str">
-        <f t="shared" ref="B3:B21" si="0">_xlfn.TEXTJOIN(";",TRUE,C3:I3)</f>
-        <v>Viewed;Clicked;Submit Form</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C3:I3)</f>
+        <v>Sent;Received;Clicked</v>
       </c>
       <c r="C3" t="s">
         <v>993</v>
@@ -15622,71 +15619,56 @@
       <c r="D3" t="s">
         <v>994</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>995</v>
       </c>
       <c r="I3" s="23"/>
-      <c r="J3" t="str">
-        <f>_xlfn.XLOOKUP(A3,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Content Syndication</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" hidden="1">
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="41" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B4" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Page View;Link Click;Submit Form;Watch Video;Download;Live Chat?</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C4:I4)</f>
+        <v>Viewed;Clicked;Submit Form</v>
       </c>
       <c r="C4" t="s">
+        <v>992</v>
+      </c>
+      <c r="D4" t="s">
+        <v>995</v>
+      </c>
+      <c r="E4" t="s">
         <v>996</v>
       </c>
-      <c r="D4" t="s">
-        <v>997</v>
-      </c>
-      <c r="E4" t="s">
-        <v>995</v>
-      </c>
-      <c r="F4" t="s">
-        <v>998</v>
-      </c>
-      <c r="G4" t="s">
-        <v>999</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1000</v>
-      </c>
       <c r="I4" s="23"/>
-      <c r="J4" t="str">
-        <f>_xlfn.XLOOKUP(A4,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Web</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" hidden="1">
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="41" t="s">
-        <v>951</v>
+        <v>964</v>
       </c>
       <c r="B5" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Viewed</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C5:I5)</f>
+        <v>Sent;Received;Bounced</v>
       </c>
       <c r="C5" t="s">
         <v>993</v>
       </c>
+      <c r="D5" t="s">
+        <v>994</v>
+      </c>
+      <c r="E5" t="s">
+        <v>997</v>
+      </c>
       <c r="I5" s="23"/>
-      <c r="J5" t="str">
-        <f>_xlfn.XLOOKUP(A5,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Above the Line - Non Digital</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" hidden="1">
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="41" t="s">
-        <v>954</v>
+        <v>967</v>
       </c>
       <c r="B6" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Viewed;Clicked;Responded</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C6:I6)</f>
+        <v>Sent;Received;Bounced;Opened;Clicked;Opt-Out;Responded</v>
       </c>
       <c r="C6" t="s">
         <v>993</v>
@@ -15695,47 +15677,44 @@
         <v>994</v>
       </c>
       <c r="E6" t="s">
+        <v>997</v>
+      </c>
+      <c r="F6" t="s">
+        <v>998</v>
+      </c>
+      <c r="G6" t="s">
+        <v>995</v>
+      </c>
+      <c r="H6" t="s">
+        <v>999</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="41" t="s">
+        <v>962</v>
+      </c>
+      <c r="B7" s="39" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,C7:I7)</f>
+        <v>Registered;Attended</v>
+      </c>
+      <c r="C7" t="s">
         <v>1001</v>
       </c>
-      <c r="I6" s="23"/>
-      <c r="J6" t="str">
-        <f>_xlfn.XLOOKUP(A6,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Social Posts</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" hidden="1">
-      <c r="A7" s="41" t="s">
-        <v>955</v>
-      </c>
-      <c r="B7" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Viewed;Clicked;Responded;Opt-Out</v>
-      </c>
-      <c r="C7" t="s">
-        <v>993</v>
-      </c>
       <c r="D7" t="s">
-        <v>994</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F7" t="s">
         <v>1002</v>
       </c>
       <c r="I7" s="23"/>
-      <c r="J7" t="str">
-        <f>_xlfn.XLOOKUP(A7,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Social Outbound Messages</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" hidden="1">
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="41" t="s">
-        <v>959</v>
+        <v>984</v>
       </c>
       <c r="B8" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Registered;Attended;View on Demand</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C8:I8)</f>
+        <v>Called;Not Answered</v>
       </c>
       <c r="C8" t="s">
         <v>1003</v>
@@ -15743,410 +15722,350 @@
       <c r="D8" t="s">
         <v>1004</v>
       </c>
-      <c r="E8" t="s">
+      <c r="I8" s="23"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="41" t="s">
+        <v>973</v>
+      </c>
+      <c r="B9" s="39" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,C9:I9)</f>
+        <v>Sent;Received;Bounced;Clicked;Responsed;Opt-Out</v>
+      </c>
+      <c r="C9" t="s">
+        <v>993</v>
+      </c>
+      <c r="D9" t="s">
+        <v>994</v>
+      </c>
+      <c r="E9" t="s">
+        <v>997</v>
+      </c>
+      <c r="F9" t="s">
+        <v>995</v>
+      </c>
+      <c r="G9" t="s">
         <v>1005</v>
       </c>
-      <c r="I8" s="23"/>
-      <c r="J8" t="str">
-        <f>_xlfn.XLOOKUP(A8,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Virtual Events</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" hidden="1">
-      <c r="A9" s="41" t="s">
-        <v>962</v>
-      </c>
-      <c r="B9" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Registered;Attended</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1004</v>
+      <c r="H9" t="s">
+        <v>999</v>
       </c>
       <c r="I9" s="23"/>
-      <c r="J9" t="str">
-        <f>_xlfn.XLOOKUP(A9,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>F2F Events</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" hidden="1">
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="41" t="s">
-        <v>963</v>
+        <v>978</v>
       </c>
       <c r="B10" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Registered;Attended;View on Demand</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C10:I10)</f>
+        <v>Initiated;Answered;Disconnected</v>
       </c>
       <c r="C10" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D10" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="E10" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I10" s="23"/>
-      <c r="J10" t="str">
-        <f>_xlfn.XLOOKUP(A10,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Webinars</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" hidden="1">
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="41" t="s">
-        <v>964</v>
+        <v>938</v>
       </c>
       <c r="B11" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Sent;Received;Bounced</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C11:I11)</f>
+        <v>Viewed;Clicked;Submit Form</v>
       </c>
       <c r="C11" t="s">
-        <v>1006</v>
+        <v>992</v>
       </c>
       <c r="D11" t="s">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="E11" t="s">
-        <v>1008</v>
+        <v>996</v>
       </c>
       <c r="I11" s="23"/>
-      <c r="J11" t="str">
-        <f>_xlfn.XLOOKUP(A11,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Direct Mail</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" hidden="1">
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="41" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B12" s="39" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,C12:I12)</f>
-        <v>Sent;Received;Read;Clicked;Responded;Opt-Out</v>
+        <v>Sent;Received;Read;Clicked;Responded;Opt-Out;Opened</v>
       </c>
       <c r="C12" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="D12" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="E12" t="s">
         <v>1009</v>
       </c>
       <c r="F12" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="G12" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="s">
-        <v>1002</v>
-      </c>
-      <c r="I12" s="23"/>
-      <c r="J12" t="str">
-        <f>_xlfn.XLOOKUP(A12,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Whatsapp</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" hidden="1">
+        <v>999</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="41" t="s">
-        <v>966</v>
+        <v>982</v>
       </c>
       <c r="B13" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Sent;Received;Read;Clicked;Responded;Opt-Out</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C13:I13)</f>
+        <v>Dialled;Answered;Engaged</v>
       </c>
       <c r="C13" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="D13" t="s">
         <v>1007</v>
       </c>
       <c r="E13" t="s">
-        <v>1009</v>
-      </c>
-      <c r="F13" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I13" s="23"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="41" t="s">
+        <v>983</v>
+      </c>
+      <c r="B14" s="39" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,C14:I14)</f>
+        <v>Sent;Received;Bounced;Opened;Clicked;Opt-Out;Responded</v>
+      </c>
+      <c r="C14" t="s">
+        <v>993</v>
+      </c>
+      <c r="D14" t="s">
         <v>994</v>
       </c>
-      <c r="G13" t="s">
-        <v>1001</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="E14" t="s">
+        <v>997</v>
+      </c>
+      <c r="F14" t="s">
+        <v>998</v>
+      </c>
+      <c r="G14" t="s">
+        <v>995</v>
+      </c>
+      <c r="H14" t="s">
+        <v>999</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="41" t="s">
+        <v>980</v>
+      </c>
+      <c r="B15" s="39" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,C15:I15)</f>
+        <v>Invited;Attended</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D15" t="s">
         <v>1002</v>
       </c>
-      <c r="I13" s="23"/>
-      <c r="J13" t="str">
-        <f>_xlfn.XLOOKUP(A13,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>RCS</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" hidden="1">
-      <c r="A14" s="41" t="s">
-        <v>967</v>
-      </c>
-      <c r="B14" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Sent;Received;Bounced;Opened;Clicked;Opt-Out;Responded</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="I15" s="23"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="41" t="s">
+        <v>970</v>
+      </c>
+      <c r="B16" s="39" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,C16:I16)</f>
+        <v>Sent;Received;Bounced;Clicked;Responsed;Opt-Out</v>
+      </c>
+      <c r="C16" t="s">
+        <v>993</v>
+      </c>
+      <c r="D16" t="s">
         <v>994</v>
       </c>
-      <c r="H14" t="s">
-        <v>1002</v>
-      </c>
-      <c r="I14" s="23" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J14" t="str">
-        <f>_xlfn.XLOOKUP(A14,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Email</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" hidden="1">
-      <c r="A15" s="41" t="s">
-        <v>970</v>
-      </c>
-      <c r="B15" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Sent;Received;Bounced;Clicked;Responsed;Opt-Out</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F15" t="s">
-        <v>994</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1011</v>
-      </c>
-      <c r="H15" t="s">
-        <v>1002</v>
-      </c>
-      <c r="I15" s="23"/>
-      <c r="J15" t="str">
-        <f>_xlfn.XLOOKUP(A15,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>SMS</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" hidden="1">
-      <c r="A16" s="41" t="s">
-        <v>973</v>
-      </c>
-      <c r="B16" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Sent;Received;Bounced;Clicked;Responsed;Opt-Out</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1007</v>
-      </c>
       <c r="E16" t="s">
-        <v>1008</v>
+        <v>997</v>
       </c>
       <c r="F16" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="G16" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="H16" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="I16" s="23"/>
-      <c r="J16" t="str">
-        <f>_xlfn.XLOOKUP(A16,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>MMS</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" hidden="1">
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="41" t="s">
-        <v>974</v>
+        <v>955</v>
       </c>
       <c r="B17" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Sent;Received;Clicked</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C17:I17)</f>
+        <v>Viewed;Clicked;Responded;Opt-Out</v>
       </c>
       <c r="C17" t="s">
-        <v>1006</v>
+        <v>992</v>
       </c>
       <c r="D17" t="s">
-        <v>1007</v>
+        <v>995</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1000</v>
       </c>
       <c r="F17" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="I17" s="23"/>
-      <c r="J17" t="str">
-        <f>_xlfn.XLOOKUP(A17,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>App Push Notification</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" hidden="1">
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="41" t="s">
-        <v>980</v>
+        <v>954</v>
       </c>
       <c r="B18" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Invited;Attended</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C18:I18)</f>
+        <v>Viewed;Clicked;Responded</v>
       </c>
       <c r="C18" t="s">
-        <v>1012</v>
+        <v>992</v>
       </c>
       <c r="D18" t="s">
-        <v>1004</v>
+        <v>995</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1000</v>
       </c>
       <c r="I18" s="23"/>
-      <c r="J18" t="str">
-        <f>_xlfn.XLOOKUP(A18,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Sales Meetings</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" hidden="1">
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="41" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="B19" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Dialled;Answered;Engaged</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C19:I19)</f>
+        <v>Attempted;Answered;Conversed</v>
       </c>
       <c r="C19" t="s">
         <v>1013</v>
       </c>
       <c r="D19" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E19" t="s">
         <v>1014</v>
       </c>
-      <c r="E19" t="s">
+      <c r="I19" s="23"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="41" t="s">
+        <v>959</v>
+      </c>
+      <c r="B20" s="39" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,C20:I20)</f>
+        <v>Registered;Attended;View on Demand</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E20" t="s">
         <v>1015</v>
       </c>
-      <c r="I19" s="23"/>
-      <c r="J19" t="str">
-        <f>_xlfn.XLOOKUP(A19,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Sales Calls</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" hidden="1">
-      <c r="A20" s="41" t="s">
-        <v>983</v>
-      </c>
-      <c r="B20" s="39" t="str">
-        <f t="shared" si="0"/>
-        <v>Sent;Received;Bounced;Opened;Clicked;Opt-Out;Responded</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F20" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G20" t="s">
-        <v>994</v>
-      </c>
-      <c r="H20" t="s">
-        <v>1002</v>
-      </c>
-      <c r="I20" s="23" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J20" t="str">
-        <f>_xlfn.XLOOKUP(A20,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Sales Email</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="I20" s="23"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="42" t="s">
-        <v>984</v>
+        <v>947</v>
       </c>
       <c r="B21" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>Called</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C21:I21)</f>
+        <v>Page View;Link Click;Submit Form;Watch Video;Download;Live Chat?</v>
       </c>
       <c r="C21" s="24" t="s">
         <v>1016</v>
       </c>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
+      <c r="D21" s="24" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>996</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>1019</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>1020</v>
+      </c>
       <c r="I21" s="25"/>
-      <c r="J21" t="str">
-        <f>_xlfn.XLOOKUP(A21,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Inbound Calls</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" hidden="1">
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="41" t="s">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="B22" s="39" t="str">
-        <f t="shared" ref="B22:B23" si="1">_xlfn.TEXTJOIN(";",TRUE,C22:I22)</f>
-        <v>Attempted;Answered;Conversed</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C22:I22)</f>
+        <v>Registered;Attended;View on Demand</v>
       </c>
       <c r="C22" t="s">
-        <v>1017</v>
+        <v>1001</v>
       </c>
       <c r="D22" t="s">
-        <v>1014</v>
+        <v>1002</v>
       </c>
       <c r="E22" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="I22" s="23"/>
-      <c r="J22" t="str">
-        <f>_xlfn.XLOOKUP(A22,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Telemarketing</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" hidden="1">
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="41" t="s">
-        <v>978</v>
+        <v>965</v>
       </c>
       <c r="B23" s="39" t="str">
-        <f t="shared" si="1"/>
-        <v>Initiated;Answered;Disconnected</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,C23:I23)</f>
+        <v>Sent;Received;Read;Clicked;Responded;Opt-Out</v>
       </c>
       <c r="C23" t="s">
-        <v>1019</v>
+        <v>993</v>
       </c>
       <c r="D23" t="s">
-        <v>1014</v>
+        <v>994</v>
       </c>
       <c r="E23" t="s">
-        <v>1020</v>
+        <v>1009</v>
+      </c>
+      <c r="F23" t="s">
+        <v>995</v>
+      </c>
+      <c r="G23" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H23" t="s">
+        <v>999</v>
       </c>
       <c r="I23" s="23"/>
-      <c r="J23" t="str">
-        <f>_xlfn.XLOOKUP(A23,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
-        <v>Online Chat</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16157,14 +16076,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D1F78A46A5B61544A3F5E5F9D558353B" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cd5889db134979e54dcf054cdc4727ec">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a7019f60-298e-442e-b6f6-687001478962" xmlns:ns3="244a3a2d-c3b8-4eaa-9334-4c3b8cbc7cc9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fdf5543a8e45e11fa247a01810ff6e7b" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D1F78A46A5B61544A3F5E5F9D558353B" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="92b8702d1b18f2c7a64a1b24d1d21dde">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a7019f60-298e-442e-b6f6-687001478962" xmlns:ns3="244a3a2d-c3b8-4eaa-9334-4c3b8cbc7cc9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="605d586cb6f7e651dfebb6c8ab4a0f97" ns2:_="" ns3:_="">
     <xsd:import namespace="a7019f60-298e-442e-b6f6-687001478962"/>
     <xsd:import namespace="244a3a2d-c3b8-4eaa-9334-4c3b8cbc7cc9"/>
     <xsd:element name="properties">
@@ -16363,6 +16276,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -16373,11 +16292,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981D98BA-C602-41F7-9CF6-ADC2B2B0572D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F5815DB-96BF-430B-84BF-21F9C02EDEA0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{221E8208-2559-4473-AFD3-FB4000FD0DD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981D98BA-C602-41F7-9CF6-ADC2B2B0572D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
